--- a/important_mails_2026-03-27.xlsx
+++ b/important_mails_2026-03-27.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,37 +485,727 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Live Q&amp;A on customer feedback with experienced sellers</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Connect with sellers experienced in customer feedback
+Join us on March 31 for a live Q&amp;A event in the New Seller Community. Experienced Amazon selling partners will answer your customer feedback questions, offering insights from their own journey.
+Before the event, post your toughest questions about managing feedback, buyer-seller messaging, and customer relations.
+[Post your question](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+[An Amazon delivery driver walks next to an Amazon Prime delivery van.](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Meet our hosts
+[A checkmark icon]
+Amazon Seller: TVOI50
+Hi, my name is Tish. We’ve been selling on Amazon for 5 years in the Office Furniture category. We are FBM, an authorized re-seller for a major furniture manufacturer and strive to make every transaction a seamless one. If it’s not, our customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0FCDRNTT8, B0D7SKQ6GC
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-09</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-09 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X002A05YW5 Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- CQhO1/+c38
+ Unsellable Products:
+- FNSKU: X002C14R1B Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -531,39 +1221,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -583,39 +1273,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -641,39 +1331,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -689,39 +1379,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -742,39 +1432,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -791,39 +1481,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -838,39 +1528,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -885,39 +1575,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -936,40 +1626,40 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -988,39 +1678,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -1030,39 +1720,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1080,39 +1770,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -1128,39 +1818,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -1176,39 +1866,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1223,39 +1913,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1270,39 +1960,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1323,40 +2013,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -1371,39 +2061,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -1424,39 +2114,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -1489,203 +2179,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-02 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X002A05YW5 Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- kpCypnMqWe
- Unsellable Products:
-- FNSKU: X00265F4H9 Quantity: 1
-- FNSKU: X002C17O8J Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- AJ3wMIfu1v
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1701,39 +2227,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1747,40 +2273,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1796,39 +2322,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1848,39 +2374,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1894,39 +2420,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1946,39 +2472,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1999,39 +2525,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2051,39 +2577,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2103,40 +2629,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -2152,39 +2678,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2210,39 +2736,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2259,39 +2785,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2306,39 +2832,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2362,39 +2888,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2408,39 +2934,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2457,39 +2983,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2509,39 +3035,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2558,39 +3084,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2614,39 +3140,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2666,39 +3192,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2718,39 +3244,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2769,39 +3295,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2819,39 +3345,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2873,39 +3399,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2928,39 +3454,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2979,39 +3505,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3030,39 +3556,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3082,39 +3608,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3134,39 +3660,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3184,39 +3710,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3234,39 +3760,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3284,39 +3810,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3335,39 +3861,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3385,40 +3911,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3436,39 +3962,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3486,39 +4012,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3536,39 +4062,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3583,39 +4109,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3631,39 +4157,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3681,39 +4207,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3731,39 +4257,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3781,195 +4307,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Submit UK import details by 26/04/2026 to avoid shipping
- restrictions</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit UK import details by 26/04/2026 to avoid shipping restrictions
- Hello Weihai EU,
- Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 26/04/2026 to continue creating new UK shipments.
- Why is this happening?
- We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
- Where do I enter my Import Entry Numbers (IEN)?
- To enter the IENs for your applicable shipments:
-- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
-- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
-- Save your IEN entry.
- If you would need to update your IEN, you can follow the above steps again.
- What happens if I don’t submit these details?
- You have 60 days after first re</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
- Hello,
- You can now submit Product Safety Law (PSL) compliance information through the listing workflow for new listings, or through Manage All Inventory for existing listings.
- In November 2024, Saudi Arabia implemented the PSL, which applies to most consumer products sold in Saudi Arabia, except those regulated by the Saudi Food and Drug Authority (SFDA).
- To ensure you’re compliant, we recommend that you submit the following information as soon as possible:
-- Email or URL of the manufacturer
-- Email or URL of the importer if applicable, or your authorized representative in Saudi Arabia
-- Safety information, warnings, safety images or disclaimers
-- Proof of your product’s compliance with applicable Saudi technical standards For more information, go to Product Safety Law (PSL) .
- The Amazon Services team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -3985,39 +4355,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4033,39 +4403,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4083,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4132,39 +4502,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4188,39 +4558,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4235,39 +4605,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4283,39 +4653,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4332,40 +4702,40 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4381,39 +4751,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4433,39 +4803,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4481,40 +4851,40 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4530,39 +4900,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4579,39 +4949,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4630,39 +5000,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4680,39 +5050,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4724,39 +5094,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4768,39 +5138,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4812,39 +5182,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4856,39 +5226,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4900,39 +5270,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4944,39 +5314,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4988,39 +5358,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5032,39 +5402,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5082,39 +5452,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5157,39 +5527,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5206,40 +5576,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5257,39 +5627,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5307,39 +5677,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5351,39 +5721,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5395,39 +5765,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5446,39 +5816,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5490,39 +5860,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5534,39 +5904,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5578,39 +5948,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5622,39 +5992,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5666,39 +6036,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5710,39 +6080,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5754,39 +6124,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5798,39 +6168,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5842,40 +6212,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5894,39 +6264,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5938,40 +6308,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5983,39 +6353,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6027,39 +6397,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6078,39 +6448,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6122,39 +6492,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6173,39 +6543,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6217,39 +6587,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6265,40 +6635,40 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6316,39 +6686,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6366,39 +6736,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6414,39 +6784,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6464,39 +6834,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6537,39 +6907,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6587,40 +6957,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6638,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6687,39 +7057,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6737,39 +7107,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6787,39 +7157,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6834,39 +7204,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6880,39 +7250,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6928,39 +7298,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6976,39 +7346,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7025,40 +7395,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7074,39 +7444,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -7135,39 +7505,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7184,40 +7554,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7234,39 +7604,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7281,40 +7651,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7329,39 +7699,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7376,39 +7746,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7423,146 +7793,203 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-04-02</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 02/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
- 119.06 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de
-análisis ha señalado que una asociación con usted sería una gran oportunidad
-para ambos.
-¿Estaría
-disponible para una reunión online esta semana?
-Acerca de Worten
-- Somos el líder del mercado portugués:
-- Nº 1 del
-comercio electrónico portugués
-- Sitio web con
-mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200
-tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de
-gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes los 6 meses iniciales
-Estaré encantado
-de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos
-Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-04-02 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: X002A05YW5 Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- kpCypnMqWe
+ Unsellable Products:
+- FNSKU: X00265F4H9 Quantity: 1
+- FNSKU: X002C17O8J Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- AJ3wMIfu1v
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7585,39 +8012,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7639,39 +8066,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7694,39 +8121,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7749,39 +8176,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7807,39 +8234,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7861,39 +8288,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7917,40 +8344,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7969,40 +8396,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8020,39 +8447,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8066,39 +8493,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8116,39 +8543,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8165,39 +8592,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8215,40 +8642,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8267,39 +8694,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8315,39 +8742,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8377,40 +8804,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8429,40 +8856,40 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8480,39 +8907,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.

--- a/important_mails_2026-03-27.xlsx
+++ b/important_mails_2026-03-27.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1175,37 +1175,85 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>[Action Required] – Update Inventory -FBA</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
+We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
+https://sellercentral.amazon.ca/restockinventory/recommendations
+Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
+B0DMFL5X12, B0D7QHCF8J
+You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
+For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
+If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+If you are not the correct point of contact, please re-direct this report to the correct point of contact.
+If you wish to unsubscribe please REPLY ALL with the subject l</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1221,39 +1269,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1273,39 +1321,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1331,39 +1379,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1379,39 +1427,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1432,39 +1480,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -1481,39 +1529,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1528,39 +1576,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1575,39 +1623,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1626,40 +1674,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -1678,39 +1726,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -1720,39 +1768,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1767,54 +1815,6 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
 -
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
-We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0F13M1H6F, B0D97JS8WD
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.ca/fixyourproducts/drafts
-To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
- https://sellercentral.amazon.ca/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
         </is>
       </c>
     </row>
@@ -3262,21 +3262,69 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
+We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0F13M1H6F, B0D97JS8WD
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.ca/fixyourproducts/drafts
+To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+ https://sellercentral.amazon.ca/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3295,39 +3343,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3345,39 +3393,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3399,39 +3447,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3454,39 +3502,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3505,39 +3553,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3556,39 +3604,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3608,39 +3656,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3660,39 +3708,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3710,39 +3758,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3760,39 +3808,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3810,39 +3858,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3861,39 +3909,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3911,40 +3959,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3962,39 +4010,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4012,39 +4060,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -4062,39 +4110,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4109,39 +4157,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4157,39 +4205,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4207,39 +4255,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -4257,39 +4305,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4307,39 +4355,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4355,39 +4403,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4403,39 +4451,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4453,39 +4501,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4502,39 +4550,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4558,39 +4606,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4605,39 +4653,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4653,39 +4701,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4702,40 +4750,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4751,39 +4799,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4803,39 +4851,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4851,40 +4899,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4900,39 +4948,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4949,39 +4997,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5000,39 +5048,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5050,39 +5098,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -5094,39 +5142,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5138,39 +5186,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5182,39 +5230,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5226,39 +5274,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5270,39 +5318,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5314,39 +5362,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5358,39 +5406,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5402,39 +5450,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5452,39 +5500,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5527,39 +5575,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5576,40 +5624,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5627,39 +5675,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5677,39 +5725,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5721,39 +5769,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5765,39 +5813,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5816,39 +5864,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5860,39 +5908,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5904,39 +5952,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5948,39 +5996,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5992,39 +6040,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6036,39 +6084,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6080,39 +6128,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6124,39 +6172,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6168,39 +6216,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6212,40 +6260,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6264,39 +6312,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6308,40 +6356,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6353,39 +6401,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6397,39 +6445,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6448,39 +6496,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6492,39 +6540,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6543,39 +6591,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6587,39 +6635,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6635,40 +6683,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6686,39 +6734,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6736,39 +6784,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6784,39 +6832,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6834,39 +6882,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6907,39 +6955,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6957,40 +7005,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7008,39 +7056,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7057,39 +7105,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7107,39 +7155,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7157,39 +7205,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -7204,39 +7252,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -7250,39 +7298,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7298,39 +7346,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -7346,39 +7394,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7395,40 +7443,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7444,39 +7492,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -7505,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7554,40 +7602,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7604,39 +7652,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7651,40 +7699,40 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7699,39 +7747,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7746,39 +7794,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7793,39 +7841,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7846,39 +7894,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7902,39 +7950,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7957,39 +8005,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8012,39 +8060,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8066,39 +8114,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8121,39 +8169,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8176,39 +8224,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -8234,39 +8282,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8288,39 +8336,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8344,40 +8392,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8396,40 +8444,40 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8447,39 +8495,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8493,39 +8541,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8543,39 +8591,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8592,39 +8640,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8642,40 +8690,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8694,39 +8742,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8742,39 +8790,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8804,40 +8852,40 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8856,40 +8904,40 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8907,39 +8955,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
